--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1,266 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27930" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>parent</t>
-  </si>
-  <si>
-    <t>valueType</t>
-  </si>
-  <si>
-    <t>sep</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*fields</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>variants</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>分割符</t>
-  </si>
-  <si>
-    <t>字段名</t>
-  </si>
-  <si>
-    <t>字段别名</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>字段变体</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -560,170 +471,171 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="23" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="22" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -777,11 +689,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1041,195 +1016,557 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P23"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5083333333333" customWidth="1"/>
-    <col min="13" max="13" width="10.3833333333333" customWidth="1"/>
+    <col width="20.625" customWidth="1" style="5" min="2" max="4"/>
+    <col width="12.25" customWidth="1" style="5" min="5" max="6"/>
+    <col width="15" customWidth="1" style="5" min="7" max="9"/>
+    <col width="13.5083333333333" customWidth="1" style="5" min="10" max="12"/>
+    <col width="10.3833333333333" customWidth="1" style="5" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="B4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="B6" s="3"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>valueType</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>sep</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>*fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>variants</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>分割符</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>字段名</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>字段别名</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>字段变体</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Level.LevelSpawnRecipe</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MonsterEntityId</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Entity.EntityId</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>可读怪物实体枚举；唯一关联怪物配置与实体资源</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>SpawnPointId</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>场景生成点的稳定 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="n"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>首次延迟秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>生成间隔秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Level.LevelStage</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>StageOrder</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>从 1 连续递增，与阶段列表行序一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>阶段名</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Activation</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Level.StageActivation</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>CameraArrived=相机右缘抵达阶段右界；Trigger=特殊区域激活</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>TriggerId</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>仅 Trigger 阶段填写，其他阶段留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>GateId</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>阶段右界门 ID；最后阶段可留空，使用关卡右墙</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MaxActive</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>最大并存数</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>SpawnDelay</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>阶段启动后开始生成的延迟（秒），与各配方 Delay 相加</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Recipes</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>list,Level.LevelSpawnRecipe</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>同阶段配方并行；每行一条独立生成流</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Level.LevelConfig</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>LevelId</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>关卡ID（主键）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>LegacyId</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>旧项目关卡编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>NameCn</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>关卡名</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>关卡说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>ScenePath</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>场景资源路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>PlayerSpawnPointId</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>玩家出生点ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Stages</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>list,Level.LevelStage</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>阶段列表（多行：每行一个阶段；配方续行阶段列留空）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="5" min="2" max="4"/>
@@ -1562,6 +1562,784 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stat.StatBlock</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>一组完整属性值；英雄逐级成长行与怪物配置共用</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>生命上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MaxMp</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>魔法上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>物防</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Mdef</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>魔防</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>暴击</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>闪避</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Lucky</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>幸运(加暴击倍率)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>韧性(减对方幸运)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Htarget</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>命中(减对方闪避)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>CritReduce</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>暴击抵抗</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Ar</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>破甲(减对方物防)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sp</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>破魔(减对方魔防)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Vampirism</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>吸血(百分点,伤害转生命)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>HpRegen</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>每秒回血</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>MpRegen</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>每秒回蓝</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hero.HeroGrowthConfig</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>英雄逐级属性（HeroId + Level 联合主键）</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>HeroId</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>英雄ID(对应 HeroConfig.Id)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>等级(1 起连续，覆盖经验表全部等级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Stat.StatBlock</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>该等级的成长属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Monster.MonsterConfig</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>怪物配置（怪物无成长，Level 只用于等级压制）</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>怪物ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>LegacyId</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>旧怪物编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>NameCn</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>中文名</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>EntityId</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Entity.EntityId</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>实体枚举</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>等级(参与等级压制)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Stat.StatBlock</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>战斗属性(攻击 Power 填 0：怪物伤害由招式 FlatPower 决定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>移动速度 px/s(旧 speed=8,代码里×10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>SightRange</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>索敌距离(旧 mysee)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>AttackDesire</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>攻击欲望 0-100(旧 attackDesire)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>BehitCalmTime</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>受击后僵直秒数(旧 behit_calmtime)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>AddExp</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>击杀给英雄的经验(旧 add_exp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>HurtSoundId</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>DeathSoundId</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>死亡语音(同上)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>重力 px/s²(旧 gravity=980 向下)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PatrolInterval</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>巡逻重新决策间隔秒(旧 change_state 计时器 3s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PatrolIdleChance</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PatrolRadius</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>AttackInterval</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>AttackFirstDelay</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>vector2</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>进入攻击范围后首次出手判定的随机延迟秒(x=最短,y=最长);出手是概率判定,这里只是反应时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Monster.MonsterRank</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>SuperArmor</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>AttackRangeSlack</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>LoseTargetTime</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PaceRange</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="5" min="2" max="4"/>
@@ -1343,44 +1343,34 @@
     <row r="13">
       <c r="J13" s="4" t="inlineStr">
         <is>
+          <t>LeftGateId</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>阶段左界门 ID；空使用关卡左墙；允许与上一阶段区域重叠</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
           <t>GateId</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>阶段右界门 ID；最后阶段可留空，使用关卡右墙</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MaxActive</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>最大并存数</t>
+          <t>阶段右界门 ID；空使用关卡右墙；不再推导下一阶段左界</t>
         </is>
       </c>
     </row>
@@ -1395,19 +1385,19 @@
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>SpawnDelay</t>
+          <t>MaxActive</t>
         </is>
       </c>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>阶段启动后开始生成的延迟（秒），与各配方 Delay 相加</t>
+          <t>最大并存数</t>
         </is>
       </c>
     </row>
@@ -1422,82 +1412,92 @@
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Recipes</t>
+          <t>SpawnDelay</t>
         </is>
       </c>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>list,Level.LevelSpawnRecipe</t>
+          <t>float</t>
         </is>
       </c>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="inlineStr">
         <is>
+          <t>阶段启动后开始生成的延迟（秒），与各配方 Delay 相加</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Recipes</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>list,Level.LevelSpawnRecipe</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
           <t>同阶段配方并行；每行一条独立生成流</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Level.LevelConfig</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>LevelId</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>关卡ID（主键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>LegacyId</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>旧项目关卡编号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>NameCn</t>
+          <t>LegacyId</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>关卡名</t>
+          <t>旧项目关卡编号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t>NameCn</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1507,14 +1507,14 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>关卡说明</t>
+          <t>关卡名</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>ScenePath</t>
+          <t>Desc</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1524,817 +1524,851 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>场景资源路径</t>
+          <t>关卡说明</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="J22" s="4" t="inlineStr">
         <is>
+          <t>ScenePath</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>场景资源路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MusicId</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>本关背景音乐；由关卡流程通过 GGF 声音配置播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
           <t>PlayerSpawnPointId</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>玩家出生点ID</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="J23" s="4" t="inlineStr">
+    <row r="25">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Stages</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>list,Level.LevelStage</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>阶段列表（多行：每行一个阶段；配方续行阶段列留空）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Stat.StatBlock</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>一组完整属性值；英雄逐级成长行与怪物配置共用</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>MaxHp</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>生命上限</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="J25" t="inlineStr">
+    <row r="27">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>MaxMp</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>魔法上限</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="J26" t="inlineStr">
+    <row r="28">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="J27" t="inlineStr">
+    <row r="29">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>Def</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>物防</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="J28" t="inlineStr">
+    <row r="30">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>Mdef</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>魔防</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="J29" t="inlineStr">
+    <row r="31">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>Crit</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>暴击</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="J30" t="inlineStr">
+    <row r="32">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>闪避</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="J31" t="inlineStr">
+    <row r="33">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>Lucky</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>幸运(加暴击倍率)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="J32" t="inlineStr">
+    <row r="34">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>Toughness</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>韧性(减对方幸运)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="J33" t="inlineStr">
+    <row r="35">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Htarget</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>命中(减对方闪避)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="J34" t="inlineStr">
+    <row r="36">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>CritReduce</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>暴击抵抗</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="J35" t="inlineStr">
+    <row r="37">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>Ar</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>破甲(减对方物防)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="J36" t="inlineStr">
+    <row r="38">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>Sp</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>破魔(减对方魔防)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="J37" t="inlineStr">
+    <row r="39">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Vampirism</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>吸血(百分点,伤害转生命)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="J38" t="inlineStr">
+    <row r="40">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>HpRegen</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>每秒回血</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="J39" t="inlineStr">
+    <row r="41">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>MpRegen</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>每秒回蓝</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Hero.HeroGrowthConfig</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>英雄逐级属性（HeroId + Level 联合主键）</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>HeroId</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>英雄ID(对应 HeroConfig.Id)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="J41" t="inlineStr">
+    <row r="43">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>等级(1 起连续，覆盖经验表全部等级)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="J42" t="inlineStr">
+    <row r="44">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>Stats</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>Stat.StatBlock</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>该等级的成长属性</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Monster.MonsterConfig</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>怪物配置（怪物无成长，Level 只用于等级压制）</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>怪物ID</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="J44" t="inlineStr">
+    <row r="46">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>LegacyId</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>旧怪物编号</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="J45" t="inlineStr">
+    <row r="47">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>NameCn</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>中文名</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="J46" t="inlineStr">
+    <row r="48">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="J47" t="inlineStr">
+    <row r="49">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
         <is>
           <t>Entity.EntityId</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N49" s="4" t="inlineStr">
         <is>
           <t>实体枚举</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="J48" t="inlineStr">
+    <row r="50">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
         <is>
           <t>等级(参与等级压制)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="J49" t="inlineStr">
+    <row r="51">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>Stats</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
         <is>
           <t>Stat.StatBlock</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>战斗属性(攻击 Power 填 0：怪物伤害由招式 FlatPower 决定)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="J50" t="inlineStr">
+    <row r="52">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>MoveSpeed</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>移动速度 px/s(旧 speed=8,代码里×10)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="J51" t="inlineStr">
+    <row r="53">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>SightRange</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
         <is>
           <t>索敌距离(旧 mysee)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="J52" t="inlineStr">
+    <row r="54">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>AttackDesire</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
         <is>
           <t>攻击欲望 0-100(旧 attackDesire)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="J53" t="inlineStr">
+    <row r="55">
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>BehitCalmTime</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L55" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N55" s="4" t="inlineStr">
         <is>
           <t>受击后僵直秒数(旧 behit_calmtime)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="J54" t="inlineStr">
+    <row r="56">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>AddExp</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
         <is>
           <t>击杀给英雄的经验(旧 add_exp)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="J55" t="inlineStr">
+    <row r="57">
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>HurtSoundId</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L57" s="4" t="inlineStr">
         <is>
           <t>Sound.SoundId</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N57" s="4" t="inlineStr">
         <is>
           <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="J56" t="inlineStr">
+    <row r="58">
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>DeathSoundId</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L58" s="4" t="inlineStr">
         <is>
           <t>Sound.SoundId</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N58" s="4" t="inlineStr">
         <is>
           <t>死亡语音(同上)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="J57" t="inlineStr">
+    <row r="59">
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>Gravity</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L59" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N59" s="4" t="inlineStr">
         <is>
           <t>重力 px/s²(旧 gravity=980 向下)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="J58" t="inlineStr">
+    <row r="60">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>PatrolInterval</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L60" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N60" s="4" t="inlineStr">
         <is>
           <t>巡逻重新决策间隔秒(旧 change_state 计时器 3s)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="J59" t="inlineStr">
+    <row r="61">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>PatrolIdleChance</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
         <is>
           <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="J60" t="inlineStr">
+    <row r="62">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>PatrolRadius</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="J61" t="inlineStr">
+    <row r="63">
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>AttackInterval</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L63" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N63" s="4" t="inlineStr">
         <is>
           <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="J62" t="inlineStr">
+    <row r="64">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>AttackFirstDelay</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L64" s="4" t="inlineStr">
         <is>
           <t>vector2</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>进入攻击范围后首次出手判定的随机延迟秒(x=最短,y=最长);出手是概率判定,这里只是反应时间</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="J63" t="inlineStr">
+    <row r="65">
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L65" s="4" t="inlineStr">
         <is>
           <t>Monster.MonsterRank</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N65" s="4" t="inlineStr">
         <is>
           <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="J64" t="inlineStr">
+    <row r="66">
+      <c r="J66" s="4" t="inlineStr">
         <is>
           <t>SuperArmor</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L66" s="4" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N66" s="4" t="inlineStr">
         <is>
           <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="J65" t="inlineStr">
+    <row r="67">
+      <c r="J67" s="4" t="inlineStr">
         <is>
           <t>AttackRangeSlack</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="J66" t="inlineStr">
+    <row r="68">
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>LoseTargetTime</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="N68" s="4" t="inlineStr">
         <is>
           <t>丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="J67" t="inlineStr">
+    <row r="69">
+      <c r="J69" s="4" t="inlineStr">
         <is>
           <t>PaceRange</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
         <is>
           <t>踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</t>
         </is>

--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="5" min="2" max="4"/>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>可读怪物实体枚举；唯一关联怪物配置与实体资源</t>
+          <t>可读怪物枚举，与 MonsterConfig.EntityId 一一对应</t>
         </is>
       </c>
     </row>
@@ -1268,433 +1268,433 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Level.LevelStage</t>
-        </is>
-      </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>StageOrder</t>
+          <t>HealthMultiplier</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>从 1 连续递增，与阶段列表行序一致</t>
+          <t>生命倍率；1 为基础值，必须为有限正数</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>StageName</t>
+          <t>DefenseMultiplier</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>阶段名</t>
+          <t>物理防御倍率；1 为基础值，有限且非负；不影响魔防</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Activation</t>
+          <t>AttackMultiplier</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Level.StageActivation</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>CameraArrived=相机右缘抵达阶段右界；Trigger=特殊区域激活</t>
+          <t>全部招式威力倍率；1 为基础值，有限且非负</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>TriggerId</t>
+          <t>ExperienceOverride</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>仅 Trigger 阶段填写，其他阶段留空</t>
+          <t>击败经验覆盖；-1 使用 MonsterConfig.AddExp，0 表示不给经验</t>
         </is>
       </c>
     </row>
     <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Level.LevelStage</t>
+        </is>
+      </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>LeftGateId</t>
+          <t>StageOrder</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>阶段左界门 ID；空使用关卡左墙；允许与上一阶段区域重叠</t>
+          <t>从 1 连续递增，与阶段列表行序一致</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="J14" s="4" t="inlineStr">
         <is>
+          <t>StageName</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>阶段名</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Activation</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Level.StageActivation</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>CameraArrived=相机右缘抵达阶段右界；Trigger=特殊区域激活</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>TriggerId</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>仅 Trigger 阶段填写，其他阶段留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>LeftGateId</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>阶段左界门 ID；空使用关卡左墙；允许与上一阶段区域重叠</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
           <t>GateId</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>阶段右界门 ID；空使用关卡右墙；不再推导下一阶段左界</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>MaxActive</t>
         </is>
       </c>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>最大并存数</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>SpawnDelay</t>
         </is>
       </c>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>阶段启动后开始生成的延迟（秒），与各配方 Delay 相加</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Recipes</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>list,Level.LevelSpawnRecipe</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>同阶段配方并行；每行一条独立生成流</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Level.LevelConfig</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>LevelId</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>关卡ID（主键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>LegacyId</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>旧项目关卡编号</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>NameCn</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>关卡名</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t>FeaturedOpponentId</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Entity.EntityId</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>关卡说明</t>
+          <t>本阶段需显示进场提示和血条的普通怪物；None 表示不显示</t>
         </is>
       </c>
     </row>
     <row r="22">
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>ScenePath</t>
-        </is>
-      </c>
+          <t>Recipes</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
+          <t>list,Level.LevelSpawnRecipe</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>场景资源路径</t>
+          <t>同阶段配方并行；每行一条独立生成流</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>MusicId</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>本关背景音乐；由关卡流程通过 GGF 声音配置播放</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Level.LevelConfig</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>LevelId</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>关卡ID（主键）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>PlayerSpawnPointId</t>
+          <t>LegacyId</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>玩家出生点ID</t>
+          <t>旧项目关卡编号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Stages</t>
+          <t>NameCn</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>list,Level.LevelStage</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>阶段列表（多行：每行一个阶段；配方续行阶段列留空）</t>
+          <t>关卡名</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Stat.StatBlock</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>一组完整属性值；英雄逐级成长行与怪物配置共用</t>
-        </is>
-      </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>MaxHp</t>
+          <t>Desc</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>生命上限</t>
+          <t>关卡说明</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>MaxMp</t>
+          <t>ScenePath</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>魔法上限</t>
+          <t>场景资源路径</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>MusicId</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>Sound.SoundId</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>本关背景音乐；由关卡流程通过 GGF 声音配置播放</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Def</t>
+          <t>PlayerSpawnPointId</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>物防</t>
+          <t>玩家出生点ID</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Mdef</t>
+          <t>Stages</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>list,Level.LevelStage</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>魔防</t>
+          <t>阶段列表（多行：每行一个阶段；配方续行阶段列留空）</t>
         </is>
       </c>
     </row>
     <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Stat.StatBlock</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>一组完整属性值；英雄逐级成长行与怪物配置共用</t>
+        </is>
+      </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>Crit</t>
+          <t>MaxHp</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -1704,14 +1704,14 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>暴击</t>
+          <t>生命上限</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t>MaxMp</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>闪避</t>
+          <t>魔法上限</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -1738,14 +1738,14 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>幸运(加暴击倍率)</t>
+          <t>攻击</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Def</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -1755,14 +1755,14 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>韧性(减对方幸运)</t>
+          <t>物防</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Htarget</t>
+          <t>Mdef</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -1772,14 +1772,14 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>命中(减对方闪避)</t>
+          <t>魔防</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>CritReduce</t>
+          <t>Crit</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -1789,14 +1789,14 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>暴击抵抗</t>
+          <t>暴击</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>Ar</t>
+          <t>Miss</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -1806,14 +1806,14 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>破甲(减对方物防)</t>
+          <t>闪避</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Sp</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -1823,14 +1823,14 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>破魔(减对方魔防)</t>
+          <t>幸运(加暴击倍率)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Vampirism</t>
+          <t>Toughness</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -1840,14 +1840,14 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>吸血(百分点,伤害转生命)</t>
+          <t>韧性(减对方幸运)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>HpRegen</t>
+          <t>Htarget</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>每秒回血</t>
+          <t>命中(减对方闪避)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>MpRegen</t>
+          <t>CritReduce</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -1874,24 +1874,14 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>每秒回蓝</t>
+          <t>暴击抵抗</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Hero.HeroGrowthConfig</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>英雄逐级属性（HeroId + Level 联合主键）</t>
-        </is>
-      </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>HeroId</t>
+          <t>Ar</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -1901,14 +1891,14 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>英雄ID(对应 HeroConfig.Id)</t>
+          <t>破甲(减对方物防)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Sp</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -1918,41 +1908,31 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>等级(1 起连续，覆盖经验表全部等级)</t>
+          <t>破魔(减对方魔防)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Vampirism</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>Stat.StatBlock</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>该等级的成长属性</t>
+          <t>吸血(百分点,伤害转生命)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Monster.MonsterConfig</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>怪物配置（怪物无成长，Level 只用于等级压制）</t>
-        </is>
-      </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>HpRegen</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -1962,14 +1942,14 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>怪物ID</t>
+          <t>每秒回血</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>LegacyId</t>
+          <t>MpRegen</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -1979,65 +1959,85 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>旧怪物编号</t>
+          <t>每秒回蓝</t>
         </is>
       </c>
     </row>
     <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Hero.HeroGrowthConfig</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>英雄逐级属性（HeroId + Level 联合主键）</t>
+        </is>
+      </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>NameCn</t>
+          <t>HeroId</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>英雄ID(对应 HeroConfig.Id)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>等级(1 起连续，覆盖经验表全部等级)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>EntityId</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>Entity.EntityId</t>
+          <t>Stat.StatBlock</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>实体枚举</t>
+          <t>该等级的成长属性</t>
         </is>
       </c>
     </row>
     <row r="50">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Monster.MonsterConfig</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>怪物配置（怪物无成长，Level 只用于等级压制）</t>
+        </is>
+      </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -2047,167 +2047,167 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>等级(参与等级压制)</t>
+          <t>怪物ID</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>LegacyId</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>Stat.StatBlock</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>战斗属性(攻击 Power 填 0：怪物伤害由招式 FlatPower 决定)</t>
+          <t>旧怪物编号</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>MoveSpeed</t>
+          <t>NameCn</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>移动速度 px/s(旧 speed=8,代码里×10)</t>
+          <t>中文名</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>SightRange</t>
+          <t>Desc</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>索敌距离(旧 mysee)</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>AttackDesire</t>
+          <t>EntityId</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>Entity.EntityId</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>攻击欲望 0-100(旧 attackDesire)</t>
+          <t>实体枚举</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>BehitCalmTime</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>受击后僵直秒数(旧 behit_calmtime)</t>
+          <t>等级(参与等级压制)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>AddExp</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>Stat.StatBlock</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>击杀给英雄的经验(旧 add_exp)</t>
+          <t>战斗属性(攻击 Power 填 0：怪物伤害由招式 FlatPower 决定)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>HurtSoundId</t>
+          <t>MoveSpeed</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Sound.SoundId</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
+          <t>移动速度 px/s(旧 speed=8,代码里×10)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>DeathSoundId</t>
+          <t>SightRange</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>Sound.SoundId</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>死亡语音(同上)</t>
+          <t>索敌距离(旧 mysee)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Gravity</t>
+          <t>AttackDesire</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>重力 px/s²(旧 gravity=980 向下)</t>
+          <t>攻击欲望 0-100(旧 attackDesire)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>PatrolInterval</t>
+          <t>BehitCalmTime</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -2217,14 +2217,14 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>巡逻重新决策间隔秒(旧 change_state 计时器 3s)</t>
+          <t>受击后僵直秒数(旧 behit_calmtime)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>PatrolIdleChance</t>
+          <t>AddExp</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -2234,99 +2234,99 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
+          <t>击杀给英雄的经验(旧 add_exp)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>PatrolRadius</t>
+          <t>HurtSoundId</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>Sound.SoundId</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
+          <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>AttackInterval</t>
+          <t>DeathSoundId</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>Sound.SoundId</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
+          <t>死亡语音(同上)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>AttackFirstDelay</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>vector2</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>进入攻击范围后首次出手判定的随机延迟秒(x=最短,y=最长);出手是概率判定,这里只是反应时间</t>
+          <t>重力 px/s²(旧 gravity=980 向下)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>PatrolInterval</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>Monster.MonsterRank</t>
+          <t>float</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
+          <t>巡逻重新决策间隔秒(旧 change_state 计时器 3s)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>SuperArmor</t>
+          <t>PatrolIdleChance</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
+          <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>AttackRangeSlack</t>
+          <t>PatrolRadius</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -2336,14 +2336,14 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
+          <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>LoseTargetTime</t>
+          <t>AttackInterval</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -2353,22 +2353,107 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</t>
+          <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="J69" s="4" t="inlineStr">
         <is>
+          <t>AttackFirstDelay</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>vector2</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>进入攻击范围后首次出手判定的随机延迟秒(x=最短,y=最长);出手是概率判定,这里只是反应时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>Monster.MonsterRank</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>SuperArmor</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>AttackRangeSlack</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>LoseTargetTime</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="J74" s="4" t="inlineStr">
+        <is>
           <t>PaceRange</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</t>
         </is>

--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="5" min="2" max="4"/>
@@ -2459,6 +2459,74 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>SoulPerOrb</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>每颗灵魂值（官方 gxp）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>SoulCount</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>vector2i</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>灵魂球数量闭区间（官方均匀2～4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ManaDropChance</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>蓝球掉落概率（官方12%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ManaCount</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>vector2i</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>触发后蓝球数量闭区间（官方1～3均匀）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="5" min="2" max="4"/>
@@ -2460,70 +2460,104 @@
       </c>
     </row>
     <row r="75">
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>SoulPerOrb</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
         <is>
           <t>每颗灵魂值（官方 gxp）</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>SoulCount</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L76" s="4" t="inlineStr">
         <is>
           <t>vector2i</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="N76" s="4" t="inlineStr">
         <is>
           <t>灵魂球数量闭区间（官方均匀2～4）</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="4" t="inlineStr">
         <is>
           <t>ManaDropChance</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L77" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N77" s="4" t="inlineStr">
         <is>
           <t>蓝球掉落概率（官方12%）</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="J78" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>ManaCount</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>vector2i</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>触发后蓝球数量闭区间（官方1～3均匀）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>MusouDropChance</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>白色无双球掉落概率（官方12%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>MusouCount</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>vector2i</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>触发后无双球数量闭区间（官方1～3均匀）</t>
         </is>
       </c>
     </row>
